--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2020_los_lagos.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2020_los_lagos.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:46</t>
+    <t xml:space="preserve">2026-10-05 02:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>260002.81</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>273592.38</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -877,7 +877,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>275873.12</v>
+        <v>275873.13</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>328627.06</v>
@@ -913,7 +913,7 @@
         <v>275839.16</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -921,7 +921,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>295499.12</v>
+        <v>295499.13</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>345530</v>
@@ -1108,7 +1108,7 @@
         <v>40</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>287538.62</v>
+        <v>287538.63</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>332490.59</v>
@@ -1287,7 +1287,7 @@
         <v>338178.69</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1306,7 +1306,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>342905.62</v>
+        <v>342905.63</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>400886</v>
@@ -1427,7 +1427,7 @@
         <v>69</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>372060.12</v>
+        <v>372060.13</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>432127.41</v>
@@ -1504,7 +1504,7 @@
         <v>76</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>384430.62</v>
+        <v>384430.63</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>433229.44</v>
@@ -1529,7 +1529,7 @@
         <v>381941.03</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>396037.03</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
